--- a/data/ScopingReview.xlsx
+++ b/data/ScopingReview.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cvshi\Desktop\SCOPING REVIEW\AVANCES 2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\SCOPING REVIEW\ACTUAL 2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{29F550D6-AF49-40B5-B471-391C994F0D11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5DE6C2-C243-48C1-8874-687767914C04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{1A811978-C723-4A4C-A20D-E2FDC518BA1E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1A811978-C723-4A4C-A20D-E2FDC518BA1E}"/>
   </bookViews>
   <sheets>
     <sheet name="Included" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="336">
   <si>
     <t>No.</t>
   </si>
@@ -506,9 +506,6 @@
   </si>
   <si>
     <t>Conceptual generator; lacks implementation or methodological depth in game development context.</t>
-  </si>
-  <si>
-    <t>Officially retracted due to compromised peer review and lack of editorial confidence.</t>
   </si>
   <si>
     <t>Procedural generation applied within Minecraft gameplay, not as a tool for game development.</t>
@@ -1125,7 +1122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1136,16 +1133,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1166,10 +1157,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1490,758 +1477,758 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{103ADC8C-DB03-4578-8C4C-17E58CAB9998}">
   <dimension ref="B2:D69"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="43.54296875" customWidth="1"/>
-    <col min="4" max="4" width="66.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.5546875" customWidth="1"/>
+    <col min="4" max="4" width="66.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="5" t="s">
+    <row r="2" spans="2:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B3" s="6">
+    <row r="3" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B3" s="5">
         <v>3</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B4" s="6">
+    <row r="4" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B4" s="5">
         <v>13</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B5" s="6">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B5" s="5">
         <v>15</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B6" s="6">
+    <row r="6" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B6" s="5">
         <v>23</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B7" s="6">
+    <row r="7" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B7" s="5">
         <v>24</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B8" s="6">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B8" s="5">
         <v>26</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B9" s="6">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B9" s="5">
         <v>27</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B10" s="6">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B10" s="5">
         <v>28</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B11" s="6">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B11" s="5">
         <v>29</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B12" s="6">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B12" s="5">
         <v>30</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="2:4" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B13" s="6">
+    <row r="13" spans="2:4" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B13" s="5">
         <v>34</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B14" s="5">
+        <v>36</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B14" s="6">
-        <v>36</v>
-      </c>
-      <c r="C14" s="6" t="s">
+      <c r="D14" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" s="3" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B15" s="5">
+        <v>38</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="B15" s="6">
-        <v>38</v>
-      </c>
-      <c r="C15" s="6" t="s">
+      <c r="D15" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B16" s="5">
+        <v>39</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B16" s="6">
-        <v>39</v>
-      </c>
-      <c r="C16" s="6" t="s">
+      <c r="D16" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B17" s="5">
+        <v>40</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B17" s="6">
-        <v>40</v>
-      </c>
-      <c r="C17" s="6" t="s">
+      <c r="D17" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B18" s="5">
+        <v>45</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B19" s="5">
+        <v>50</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B20" s="5">
+        <v>51</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B21" s="5">
+        <v>54</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B22" s="5">
+        <v>55</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B23" s="5">
+        <v>63</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B24" s="5">
+        <v>66</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B25" s="5">
+        <v>67</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B26" s="5">
+        <v>69</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B27" s="5">
+        <v>71</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B28" s="5">
+        <v>73</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B29" s="5">
+        <v>75</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B30" s="5">
+        <v>77</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B31" s="5">
+        <v>78</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B32" s="5">
+        <v>79</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B33" s="5">
+        <v>80</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B18" s="6">
-        <v>45</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B19" s="6">
-        <v>50</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B20" s="6">
-        <v>51</v>
-      </c>
-      <c r="C20" s="6" t="s">
+      <c r="D33" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B34" s="5">
         <v>81</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B21" s="6">
-        <v>54</v>
-      </c>
-      <c r="C21" s="6" t="s">
+      <c r="C34" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B35" s="5">
         <v>84</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B22" s="6">
-        <v>55</v>
-      </c>
-      <c r="C22" s="6" t="s">
+      <c r="C35" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="5">
         <v>86</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B23" s="6">
-        <v>63</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B24" s="6">
-        <v>66</v>
-      </c>
-      <c r="C24" s="6" t="s">
+      <c r="C36" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B37" s="5">
+        <v>89</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B38" s="5">
+        <v>91</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B39" s="5">
+        <v>96</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B40" s="5">
+        <v>97</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B41" s="5">
+        <v>101</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B42" s="5">
+        <v>104</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B43" s="5">
+        <v>105</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B44" s="5">
+        <v>111</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B45" s="5">
+        <v>120</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B46" s="5">
+        <v>121</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B47" s="5">
+        <v>123</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B48" s="5">
+        <v>124</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B49" s="5">
+        <v>125</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B50" s="5">
+        <v>126</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B51" s="5">
+        <v>127</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B52" s="5">
+        <v>130</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B53" s="5">
+        <v>131</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B54" s="5">
+        <v>133</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B55" s="5">
+        <v>134</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B56" s="5">
+        <v>135</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B57" s="5">
+        <v>137</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B58" s="5">
         <v>139</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="C58" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B59" s="5">
+        <v>141</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B60" s="5">
         <v>143</v>
       </c>
-    </row>
-    <row r="25" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B25" s="6">
-        <v>67</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D25" s="6" t="s">
+      <c r="C60" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B61" s="5">
         <v>144</v>
       </c>
-    </row>
-    <row r="26" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B26" s="6">
-        <v>69</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="D26" s="6" t="s">
+      <c r="C61" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B62" s="5">
         <v>145</v>
       </c>
-    </row>
-    <row r="27" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B27" s="6">
-        <v>71</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B28" s="6">
-        <v>73</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B29" s="6">
-        <v>75</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B30" s="6">
-        <v>77</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B31" s="6">
-        <v>78</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="B32" s="6">
-        <v>79</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B33" s="6">
-        <v>80</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B34" s="6">
-        <v>81</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B35" s="6">
-        <v>84</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="6">
-        <v>86</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B37" s="6">
-        <v>89</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B38" s="6">
-        <v>91</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B39" s="6">
-        <v>96</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B40" s="6">
-        <v>97</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="B41" s="6">
-        <v>101</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B42" s="6">
-        <v>104</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B43" s="6">
-        <v>105</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B44" s="7">
-        <v>111</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="45" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B45" s="7">
-        <v>120</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="46" spans="2:4" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B46" s="7">
-        <v>121</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="47" spans="2:4" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B47" s="7">
-        <v>123</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="48" spans="2:4" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B48" s="7">
-        <v>124</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="49" spans="2:4" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B49" s="7">
-        <v>125</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="50" spans="2:4" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B50" s="7">
-        <v>126</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="51" spans="2:4" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B51" s="7">
-        <v>127</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="52" spans="2:4" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B52" s="7">
-        <v>130</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="53" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B53" s="7">
-        <v>131</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="54" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B54" s="6">
-        <v>133</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="55" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B55" s="7">
-        <v>134</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="56" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B56" s="7">
-        <v>135</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="57" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B57" s="7">
-        <v>137</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="58" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B58" s="7">
-        <v>139</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="59" spans="2:4" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B59" s="7">
-        <v>141</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="60" spans="2:4" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B60" s="7">
-        <v>143</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="61" spans="2:4" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B61" s="7">
-        <v>144</v>
-      </c>
-      <c r="C61" s="7" t="s">
+      <c r="C62" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="D61" s="7" t="s">
+      <c r="D62" s="5" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="62" spans="2:4" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B62" s="7">
-        <v>145</v>
-      </c>
-      <c r="C62" s="7" t="s">
+    <row r="63" spans="2:4" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B63" s="5">
+        <v>146</v>
+      </c>
+      <c r="C63" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="D62" s="7" t="s">
+      <c r="D63" s="5" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="63" spans="2:4" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B63" s="7">
-        <v>146</v>
-      </c>
-      <c r="C63" s="7" t="s">
+    <row r="64" spans="2:4" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B64" s="5">
+        <v>147</v>
+      </c>
+      <c r="C64" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="D63" s="7" t="s">
+      <c r="D64" s="5" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="64" spans="2:4" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B64" s="7">
-        <v>147</v>
-      </c>
-      <c r="C64" s="7" t="s">
+    <row r="65" spans="2:4" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B65" s="5">
+        <v>148</v>
+      </c>
+      <c r="C65" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="D64" s="7" t="s">
+      <c r="D65" s="5" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="65" spans="2:4" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B65" s="7">
-        <v>148</v>
-      </c>
-      <c r="C65" s="7" t="s">
+    <row r="66" spans="2:4" s="3" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B66" s="5">
+        <v>150</v>
+      </c>
+      <c r="C66" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="D65" s="7" t="s">
+      <c r="D66" s="5" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="66" spans="2:4" s="4" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="7">
-        <v>150</v>
-      </c>
-      <c r="C66" s="7" t="s">
+    <row r="67" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B67" s="5">
+        <v>151</v>
+      </c>
+      <c r="C67" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="D66" s="7" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="67" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B67" s="6">
-        <v>151</v>
-      </c>
-      <c r="C67" s="6" t="s">
+      <c r="D67" s="5" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B68" s="5">
+        <v>152</v>
+      </c>
+      <c r="C68" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="D67" s="6" t="s">
+      <c r="D68" s="5" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="68" spans="2:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="B68" s="6">
-        <v>152</v>
-      </c>
-      <c r="C68" s="6" t="s">
+    <row r="69" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B69" s="5">
+        <v>158</v>
+      </c>
+      <c r="C69" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="D68" s="6" t="s">
+      <c r="D69" s="5" t="s">
         <v>255</v>
-      </c>
-    </row>
-    <row r="69" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B69" s="6">
-        <v>158</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -2252,1327 +2239,1320 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{395C3796-3EA7-44A4-B4ED-C3ED5B8D2BC4}">
-  <dimension ref="B2:E95"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A2:E94"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="41.08984375" customWidth="1"/>
-    <col min="5" max="5" width="48.81640625" customWidth="1"/>
+    <col min="3" max="3" width="41.109375" customWidth="1"/>
+    <col min="5" max="5" width="48.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" ht="23" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="8" t="s">
+    <row r="2" spans="1:5" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B3" s="6">
+    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B3" s="5">
         <v>1</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="6" t="s">
+      <c r="D3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B4" s="6">
+    <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B4" s="5">
         <v>2</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="D4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B5" s="6">
+    <row r="5" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B5" s="5">
         <v>4</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="D5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B6" s="6">
+    <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5">
         <v>5</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B7" s="6">
-        <v>6</v>
-      </c>
-      <c r="C7" s="6" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B7" s="5">
+        <v>6</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B8" s="6">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="5">
         <v>7</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="6" t="s">
+      <c r="D8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B9" s="6">
+    <row r="9" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B9" s="5">
         <v>8</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B10" s="6">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="5">
         <v>9</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="6" t="s">
+      <c r="D10" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B11" s="6">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="5">
         <v>10</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="6" t="s">
+      <c r="D11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B12" s="6">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B12" s="5">
         <v>11</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" s="6" t="s">
+      <c r="D12" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:5" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="6">
+    <row r="13" spans="1:5" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="5">
         <v>12</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="5" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B14" s="6">
+    <row r="14" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14" s="5">
         <v>14</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="2:5" s="2" customFormat="1" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="6">
+    <row r="15" spans="1:5" s="2" customFormat="1" ht="24.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="5">
         <v>16</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="5" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="16" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B16" s="6">
+    <row r="16" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B16" s="5">
         <v>17</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B17" s="6">
+    <row r="17" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B17" s="5">
         <v>18</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B18" s="5">
+        <v>19</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B18" s="6">
-        <v>19</v>
-      </c>
-      <c r="C18" s="6" t="s">
+      <c r="D18" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B19" s="5">
+        <v>20</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E18" s="6" t="s">
+      <c r="D19" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B20" s="5">
+        <v>21</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B21" s="5">
+        <v>22</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B22" s="5">
+        <v>25</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B23" s="5">
+        <v>31</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" s="2" customFormat="1" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="5">
+        <v>32</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" s="2" customFormat="1" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="5">
+        <v>33</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B26" s="5">
+        <v>35</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B27" s="5">
+        <v>37</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B28" s="5">
+        <v>41</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B29" s="5">
+        <v>42</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B30" s="5">
+        <v>43</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B31" s="5">
+        <v>44</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B32" s="5">
+        <v>46</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B33" s="5">
+        <v>47</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B34" s="5">
+        <v>48</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B35" s="5">
+        <v>49</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B36" s="5">
+        <v>52</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B37" s="5">
+        <v>53</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B38" s="5">
+        <v>56</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B39" s="5">
+        <v>57</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B40" s="5">
+        <v>58</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B41" s="5">
+        <v>59</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B42" s="5">
+        <v>60</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B43" s="5">
+        <v>61</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B44" s="5">
+        <v>62</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B45" s="5">
+        <v>65</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="5">
+        <v>68</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B47" s="5">
+        <v>70</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B48" s="5">
+        <v>72</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B49" s="5">
+        <v>74</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B50" s="5">
+        <v>76</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B51" s="5">
         <v>79</v>
       </c>
-    </row>
-    <row r="19" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B19" s="6">
-        <v>20</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B20" s="6">
-        <v>21</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B21" s="6">
-        <v>22</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B22" s="6">
-        <v>25</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="B23" s="6">
-        <v>31</v>
-      </c>
-      <c r="C23" s="6" t="s">
+      <c r="C51" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B52" s="5">
+        <v>82</v>
+      </c>
+      <c r="C52" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E23" s="6" t="s">
+      <c r="D52" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B53" s="5">
+        <v>83</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B54" s="5">
+        <v>85</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B55" s="5">
+        <v>87</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B56" s="5">
+        <v>88</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B57" s="5">
+        <v>90</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B58" s="5">
+        <v>92</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B59" s="5">
+        <v>93</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B60" s="5">
+        <v>94</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B61" s="5">
+        <v>95</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B62" s="5">
+        <v>98</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B63" s="5">
+        <v>99</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B64" s="5">
+        <v>100</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="65" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B65" s="5">
+        <v>102</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="66" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B66" s="5">
+        <v>103</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="67" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="5">
+        <v>106</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="68" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B68" s="5">
+        <v>107</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="69" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B69" s="5">
+        <v>108</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="70" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B70" s="5">
+        <v>109</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="71" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B71" s="5">
         <v>110</v>
       </c>
-    </row>
-    <row r="24" spans="2:5" s="2" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="6">
-        <v>32</v>
-      </c>
-      <c r="C24" s="6" t="s">
+      <c r="C71" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="72" spans="2:5" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B72" s="5">
+        <v>112</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="73" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B73" s="5">
+        <v>113</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="74" spans="2:5" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B74" s="5">
+        <v>114</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="75" spans="2:5" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B75" s="5">
+        <v>115</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="76" spans="2:5" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B76" s="5">
+        <v>116</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="77" spans="2:5" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B77" s="5">
+        <v>117</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="78" spans="2:5" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B78" s="5">
+        <v>118</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="79" spans="2:5" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B79" s="5">
+        <v>119</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="80" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B80" s="5">
         <v>122</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="C80" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A81" s="3"/>
+      <c r="B81" s="5">
+        <v>128</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="E81" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B82" s="5">
+        <v>129</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B83" s="5">
+        <v>132</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B84" s="5">
+        <v>136</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B85" s="5">
+        <v>138</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B86" s="5">
+        <v>140</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B87" s="5">
+        <v>142</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B88" s="5">
+        <v>149</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B89" s="5">
+        <v>153</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D89" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E24" s="6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" s="2" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="6">
-        <v>33</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B26" s="6">
-        <v>35</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B27" s="6">
-        <v>37</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B28" s="6">
-        <v>41</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B29" s="6">
-        <v>42</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B30" s="6">
-        <v>43</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B31" s="6">
-        <v>44</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B32" s="6">
-        <v>46</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B33" s="6">
-        <v>47</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B34" s="6">
-        <v>48</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B35" s="6">
-        <v>49</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B36" s="6">
-        <v>52</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B37" s="6">
-        <v>53</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="38" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B38" s="6">
-        <v>56</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B39" s="6">
-        <v>57</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="40" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B40" s="6">
-        <v>58</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="41" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B41" s="6">
-        <v>59</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="42" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B42" s="6">
-        <v>60</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="43" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B43" s="6">
-        <v>61</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="E43" s="6" t="s">
+      <c r="E89" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B90" s="5">
         <v>154</v>
       </c>
-    </row>
-    <row r="44" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B44" s="6">
-        <v>62</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="E44" s="6" t="s">
+      <c r="C90" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B91" s="5">
         <v>155</v>
       </c>
-    </row>
-    <row r="45" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B45" s="6">
-        <v>64</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E45" s="6" t="s">
+      <c r="C91" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E91" s="5" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B92" s="5">
         <v>156</v>
       </c>
-    </row>
-    <row r="46" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B46" s="6">
-        <v>65</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E46" s="6" t="s">
+      <c r="C92" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B93" s="5">
         <v>157</v>
       </c>
-    </row>
-    <row r="47" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="6">
-        <v>68</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="48" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B48" s="6">
-        <v>70</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="49" spans="2:5" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B49" s="6">
-        <v>72</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="50" spans="2:5" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B50" s="6">
-        <v>74</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="51" spans="2:5" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B51" s="6">
-        <v>76</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="52" spans="2:5" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B52" s="6">
-        <v>79</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="53" spans="2:5" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B53" s="6">
-        <v>82</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="54" spans="2:5" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B54" s="6">
-        <v>83</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="55" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="6">
-        <v>85</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="56" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B56" s="6">
-        <v>87</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="D56" s="6" t="s">
+      <c r="C93" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="D93" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E56" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="57" spans="2:5" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B57" s="6">
-        <v>88</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="58" spans="2:5" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B58" s="6">
-        <v>90</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="59" spans="2:5" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B59" s="6">
-        <v>92</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="D59" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="60" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B60" s="6">
-        <v>93</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="61" spans="2:5" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B61" s="6">
-        <v>94</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E61" s="6" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="62" spans="2:5" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B62" s="6">
-        <v>95</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="D62" s="6" t="s">
+      <c r="E93" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B94" s="5">
+        <v>159</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D94" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E62" s="6" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="63" spans="2:5" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B63" s="6">
-        <v>98</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="E63" s="6" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="64" spans="2:5" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B64" s="6">
-        <v>99</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E64" s="6" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="65" spans="2:5" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B65" s="6">
-        <v>100</v>
-      </c>
-      <c r="C65" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="E65" s="6" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="66" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B66" s="6">
-        <v>102</v>
-      </c>
-      <c r="C66" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="D66" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E66" s="6" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="67" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B67" s="6">
-        <v>103</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E67" s="6" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="68" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B68" s="6">
-        <v>106</v>
-      </c>
-      <c r="C68" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="D68" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E68" s="6" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="69" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B69" s="6">
-        <v>107</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E69" s="6" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="70" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B70" s="6">
-        <v>108</v>
-      </c>
-      <c r="C70" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="D70" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E70" s="6" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="71" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B71" s="6">
-        <v>109</v>
-      </c>
-      <c r="C71" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E71" s="6" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B72" s="6">
-        <v>110</v>
-      </c>
-      <c r="C72" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="D72" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E72" s="6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="73" spans="2:5" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B73" s="7">
-        <v>112</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="D73" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E73" s="7" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="74" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="6">
-        <v>113</v>
-      </c>
-      <c r="C74" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="D74" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E74" s="6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="75" spans="2:5" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B75" s="7">
-        <v>114</v>
-      </c>
-      <c r="C75" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="D75" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="E75" s="7" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="76" spans="2:5" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B76" s="7">
-        <v>115</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E76" s="7" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="77" spans="2:5" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B77" s="7">
-        <v>116</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="D77" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="E77" s="7" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="78" spans="2:5" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B78" s="7">
-        <v>117</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="D78" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="E78" s="7" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="79" spans="2:5" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B79" s="7">
-        <v>118</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="E79" s="7" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="80" spans="2:5" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B80" s="7">
-        <v>119</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="D80" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E80" s="7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="81" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B81" s="7">
-        <v>122</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="D81" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E81" s="7" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="82" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B82" s="7">
-        <v>128</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="D82" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="E82" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="83" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B83" s="7">
-        <v>129</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="D83" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E83" s="7" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="84" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B84" s="7">
-        <v>132</v>
-      </c>
-      <c r="C84" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="D84" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E84" s="7" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="85" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B85" s="7">
-        <v>136</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="D85" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E85" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="86" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B86" s="7">
-        <v>138</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="D86" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E86" s="7" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="87" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B87" s="7">
-        <v>140</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D87" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E87" s="7" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="88" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B88" s="7">
-        <v>142</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="D88" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E88" s="7" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="89" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B89" s="7">
-        <v>149</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E89" s="7" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="90" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B90" s="6">
-        <v>153</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="D90" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E90" s="6" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="91" spans="2:5" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B91" s="6">
-        <v>154</v>
-      </c>
-      <c r="C91" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="D91" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E91" s="6" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="92" spans="2:5" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B92" s="6">
-        <v>155</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="D92" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E92" s="6" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="93" spans="2:5" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B93" s="6">
-        <v>156</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="D93" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E93" s="6" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="94" spans="2:5" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B94" s="6">
-        <v>157</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="D94" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E94" s="6" t="s">
+      <c r="E94" s="5" t="s">
         <v>260</v>
-      </c>
-    </row>
-    <row r="95" spans="2:5" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="B95" s="6">
-        <v>159</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="D95" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E95" s="6" t="s">
-        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -3582,29 +3562,29 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6888C495-4788-4BF5-ABD9-3773D2DBD040}">
-  <dimension ref="B2:E12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B2:E13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="28.81640625" customWidth="1"/>
-    <col min="4" max="4" width="15.90625" customWidth="1"/>
-    <col min="5" max="5" width="34.6328125" customWidth="1"/>
+    <col min="3" max="3" width="28.77734375" customWidth="1"/>
+    <col min="4" max="4" width="15.88671875" customWidth="1"/>
+    <col min="5" max="5" width="34.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B2" s="8" t="s">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1">
         <v>12</v>
       </c>
@@ -3618,7 +3598,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
         <v>16</v>
       </c>
@@ -3632,7 +3612,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>32</v>
       </c>
@@ -3646,101 +3626,115 @@
         <v>123</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B6" s="1">
+    <row r="6" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B6" s="5">
+        <v>64</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B7" s="1">
         <v>68</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="B7" s="1">
-        <v>93</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B11" s="1">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B12" s="1">
-        <v>153</v>
+        <v>113</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B13" s="1">
+        <v>153</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>137</v>
       </c>
     </row>
